--- a/AAII_Financials/Yearly/ALVO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ALVO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>ALVO</t>
   </si>
@@ -1839,8 +1839,8 @@
       <c r="I41" s="3">
         <v>31700</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="J41" s="3">
+        <v>67400</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1917,8 +1917,8 @@
       <c r="I43" s="3">
         <v>35000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>45300</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1956,8 +1956,8 @@
       <c r="I44" s="3">
         <v>9600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="J44" s="3">
+        <v>6400</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1995,8 +1995,8 @@
       <c r="I45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>2100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2034,8 +2034,8 @@
       <c r="I46" s="3">
         <v>86200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="J46" s="3">
+        <v>122500</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2073,8 +2073,8 @@
       <c r="I47" s="3">
         <v>56700</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="J47" s="3">
+        <v>54000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2112,8 +2112,8 @@
       <c r="I48" s="3">
         <v>177000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="J48" s="3">
+        <v>170900</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2152,7 +2152,7 @@
         <v>19800</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2268,8 +2268,8 @@
       <c r="I52" s="3">
         <v>10800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>10100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2346,8 +2346,8 @@
       <c r="I54" s="3">
         <v>474400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="J54" s="3">
+        <v>374500</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2419,8 +2419,8 @@
       <c r="I57" s="3">
         <v>12000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="J57" s="3">
+        <v>11700</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2459,7 +2459,7 @@
         <v>8000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2497,8 +2497,8 @@
       <c r="I59" s="3">
         <v>14600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>24600</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2536,8 +2536,8 @@
       <c r="I60" s="3">
         <v>51000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="J60" s="3">
+        <v>54100</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2576,7 +2576,7 @@
         <v>668900</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>570600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2614,8 +2614,8 @@
       <c r="I62" s="3">
         <v>582700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>501600</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2770,8 +2770,8 @@
       <c r="I66" s="3">
         <v>1341700</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="J66" s="3">
+        <v>1142100</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2982,8 +2982,8 @@
       <c r="I72" s="3">
         <v>-1039000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="J72" s="3">
+        <v>-869000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3138,8 +3138,8 @@
       <c r="I76" s="3">
         <v>-867200</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="J76" s="3">
+        <v>-767500</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
